--- a/Defense_Platform_Business_Plan_Financial_V3.xlsx
+++ b/Defense_Platform_Business_Plan_Financial_V3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WINCODE\NDAD-Business-Plan\NDAD-Business-Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3462E410-8321-45E0-985A-02ECBF887601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E191BDF2-625E-430B-88A0-85D687415977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="817" firstSheet="10" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="817" firstSheet="4" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="28" r:id="rId1"/>
@@ -4689,8 +4689,34 @@
     <xf numFmtId="165" fontId="20" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4706,24 +4732,6 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4770,6 +4778,27 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4790,27 +4819,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4848,14 +4856,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7591,108 +7591,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="163" t="s">
         <v>942</v>
       </c>
-      <c r="B1" s="167"/>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="168"/>
-      <c r="C2" s="168"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
+      <c r="A2" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
     </row>
     <row r="3" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="210" t="s">
+      <c r="B3" s="165" t="s">
         <v>944</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
     </row>
     <row r="4" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="166" t="s">
+      <c r="B4" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
     </row>
     <row r="5" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="165" t="s">
         <v>943</v>
       </c>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
     </row>
     <row r="6" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="166" t="s">
+      <c r="B6" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="166"/>
-      <c r="D6" s="166"/>
-      <c r="E6" s="166"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
     </row>
     <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="166" t="s">
+      <c r="B7" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="166"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
     </row>
     <row r="8" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="166" t="s">
+      <c r="B8" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="166"/>
-      <c r="D8" s="166"/>
-      <c r="E8" s="166"/>
+      <c r="C8" s="162"/>
+      <c r="D8" s="162"/>
+      <c r="E8" s="162"/>
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="166"/>
-      <c r="D9" s="166"/>
-      <c r="E9" s="166"/>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
     </row>
     <row r="11" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="157" t="s">
+      <c r="A11" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="157"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
+      <c r="B11" s="161"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -7851,52 +7851,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="203" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="204" t="s">
         <v>461</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
       <c r="L2" s="103"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="201" t="s">
+      <c r="B3" s="205" t="s">
         <v>463</v>
       </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="201"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="201"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="201"/>
-      <c r="K3" s="201"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="205"/>
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
@@ -7934,19 +7934,19 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="202" t="s">
+      <c r="A6" s="206" t="s">
         <v>465</v>
       </c>
-      <c r="B6" s="202"/>
-      <c r="C6" s="202"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="105" t="s">
@@ -8207,19 +8207,19 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202" t="s">
+      <c r="A14" s="206" t="s">
         <v>473</v>
       </c>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="202"/>
-      <c r="G14" s="202"/>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="206"/>
+      <c r="I14" s="206"/>
+      <c r="J14" s="206"/>
+      <c r="K14" s="206"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
@@ -8480,19 +8480,19 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202" t="s">
+      <c r="A22" s="206" t="s">
         <v>474</v>
       </c>
-      <c r="B22" s="202"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
+      <c r="B22" s="206"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="206"/>
+      <c r="I22" s="206"/>
+      <c r="J22" s="206"/>
+      <c r="K22" s="206"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="105" t="s">
@@ -8753,19 +8753,19 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="198" t="s">
+      <c r="A30" s="202" t="s">
         <v>475</v>
       </c>
-      <c r="B30" s="198"/>
-      <c r="C30" s="198"/>
-      <c r="D30" s="198"/>
-      <c r="E30" s="198"/>
-      <c r="F30" s="198"/>
-      <c r="G30" s="198"/>
-      <c r="H30" s="198"/>
-      <c r="I30" s="198"/>
-      <c r="J30" s="198"/>
-      <c r="K30" s="198"/>
+      <c r="B30" s="202"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="202"/>
+      <c r="H30" s="202"/>
+      <c r="I30" s="202"/>
+      <c r="J30" s="202"/>
+      <c r="K30" s="202"/>
       <c r="L30" s="103"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9076,55 +9076,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="203" t="s">
+      <c r="B1" s="207" t="s">
         <v>460</v>
       </c>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="200" t="s">
+      <c r="B2" s="204" t="s">
         <v>480</v>
       </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="200"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
       <c r="N2" s="103"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C3" s="166" t="s">
+      <c r="C3" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
-      <c r="M3" s="166"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
@@ -9165,20 +9165,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="202" t="s">
+      <c r="B6" s="206" t="s">
         <v>482</v>
       </c>
-      <c r="C6" s="202"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-      <c r="M6" s="202"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="206"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="105" t="s">
@@ -9442,20 +9442,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="202" t="s">
+      <c r="B14" s="206" t="s">
         <v>483</v>
       </c>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="202"/>
-      <c r="G14" s="202"/>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-      <c r="M14" s="202"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="206"/>
+      <c r="I14" s="206"/>
+      <c r="J14" s="206"/>
+      <c r="K14" s="206"/>
+      <c r="L14" s="206"/>
+      <c r="M14" s="206"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="105" t="s">
@@ -9719,20 +9719,20 @@
       </c>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="202" t="s">
+      <c r="B22" s="206" t="s">
         <v>484</v>
       </c>
-      <c r="C22" s="202"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="202"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="206"/>
+      <c r="I22" s="206"/>
+      <c r="J22" s="206"/>
+      <c r="K22" s="206"/>
+      <c r="L22" s="206"/>
+      <c r="M22" s="206"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="105" t="s">
@@ -9996,20 +9996,20 @@
       </c>
     </row>
     <row r="30" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="202" t="s">
+      <c r="B30" s="206" t="s">
         <v>485</v>
       </c>
-      <c r="C30" s="202"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="202"/>
-      <c r="F30" s="202"/>
-      <c r="G30" s="202"/>
-      <c r="H30" s="202"/>
-      <c r="I30" s="202"/>
-      <c r="J30" s="202"/>
-      <c r="K30" s="202"/>
-      <c r="L30" s="202"/>
-      <c r="M30" s="202"/>
+      <c r="C30" s="206"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="206"/>
+      <c r="H30" s="206"/>
+      <c r="I30" s="206"/>
+      <c r="J30" s="206"/>
+      <c r="K30" s="206"/>
+      <c r="L30" s="206"/>
+      <c r="M30" s="206"/>
     </row>
     <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="105" t="s">
@@ -10605,7 +10605,7 @@
         <f>C48*C49</f>
         <v>660</v>
       </c>
-      <c r="D50" s="211" t="s">
+      <c r="D50" s="158" t="s">
         <v>945</v>
       </c>
     </row>
@@ -10706,55 +10706,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="207" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="204" t="s">
         <v>502</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
       <c r="M2" s="103"/>
     </row>
     <row r="3" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="162" t="s">
         <v>503</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
@@ -10795,20 +10795,20 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="208" t="s">
         <v>504</v>
       </c>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="208"/>
+      <c r="D6" s="208"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="208"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
+      <c r="L6" s="208"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="105" t="s">
@@ -11072,20 +11072,20 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="204" t="s">
+      <c r="A14" s="208" t="s">
         <v>505</v>
       </c>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="204"/>
-      <c r="I14" s="204"/>
-      <c r="J14" s="204"/>
-      <c r="K14" s="204"/>
-      <c r="L14" s="204"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="208"/>
+      <c r="G14" s="208"/>
+      <c r="H14" s="208"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
@@ -11349,20 +11349,20 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="204" t="s">
+      <c r="A22" s="208" t="s">
         <v>506</v>
       </c>
-      <c r="B22" s="204"/>
-      <c r="C22" s="204"/>
-      <c r="D22" s="204"/>
-      <c r="E22" s="204"/>
-      <c r="F22" s="204"/>
-      <c r="G22" s="204"/>
-      <c r="H22" s="204"/>
-      <c r="I22" s="204"/>
-      <c r="J22" s="204"/>
-      <c r="K22" s="204"/>
-      <c r="L22" s="204"/>
+      <c r="B22" s="208"/>
+      <c r="C22" s="208"/>
+      <c r="D22" s="208"/>
+      <c r="E22" s="208"/>
+      <c r="F22" s="208"/>
+      <c r="G22" s="208"/>
+      <c r="H22" s="208"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="208"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="105" t="s">
@@ -11944,7 +11944,7 @@
     <tabColor rgb="FF18A303"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1"/>
@@ -11953,58 +11953,57 @@
     <col min="13" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+    <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="207" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-    </row>
-    <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+    </row>
+    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="160" t="s">
         <v>508</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-    </row>
-    <row r="3" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+    </row>
+    <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="162" t="s">
         <v>509</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>464</v>
       </c>
@@ -12042,23 +12041,23 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="202" t="s">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="206" t="s">
         <v>510</v>
       </c>
-      <c r="B6" s="202"/>
-      <c r="C6" s="202"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="105" t="s">
         <v>466</v>
       </c>
@@ -12105,7 +12104,7 @@
         <v>125.49900398011134</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="105" t="s">
         <v>468</v>
       </c>
@@ -12152,7 +12151,7 @@
         <v>35.909999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="105" t="s">
         <v>469</v>
       </c>
@@ -12190,7 +12189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="107" t="s">
         <v>470</v>
       </c>
@@ -12235,7 +12234,7 @@
         <v>878.49302786077942</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="105" t="s">
         <v>471</v>
       </c>
@@ -12280,7 +12279,7 @@
         <v>251.36999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="108" t="s">
         <v>472</v>
       </c>
@@ -12325,23 +12324,23 @@
         <v>0.71386227092534615</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202" t="s">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="206" t="s">
         <v>511</v>
       </c>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="202"/>
-      <c r="G14" s="202"/>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="206"/>
+      <c r="I14" s="206"/>
+      <c r="J14" s="206"/>
+      <c r="K14" s="206"/>
+      <c r="L14" s="206"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
         <v>466</v>
       </c>
@@ -12388,7 +12387,7 @@
         <v>180.84631099986404</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="105" t="s">
         <v>468</v>
       </c>
@@ -12435,7 +12434,7 @@
         <v>55.65848944624895</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="105" t="s">
         <v>469</v>
       </c>
@@ -12473,7 +12472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="107" t="s">
         <v>470</v>
       </c>
@@ -12518,7 +12517,7 @@
         <v>542.53893299959213</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="105" t="s">
         <v>471</v>
       </c>
@@ -12563,7 +12562,7 @@
         <v>166.97546833874685</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="108" t="s">
         <v>472</v>
       </c>
@@ -12608,23 +12607,23 @@
         <v>0.6922332054299366</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202" t="s">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="206" t="s">
         <v>512</v>
       </c>
-      <c r="B22" s="202"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="206"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="206"/>
+      <c r="I22" s="206"/>
+      <c r="J22" s="206"/>
+      <c r="K22" s="206"/>
+      <c r="L22" s="206"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="105" t="s">
         <v>466</v>
       </c>
@@ -12671,7 +12670,7 @@
         <v>169.28</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="105" t="s">
         <v>468</v>
       </c>
@@ -12718,7 +12717,7 @@
         <v>46.278985216000002</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="105" t="s">
         <v>469</v>
       </c>
@@ -12756,7 +12755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="107" t="s">
         <v>470</v>
       </c>
@@ -12801,7 +12800,7 @@
         <v>677.12</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="105" t="s">
         <v>471</v>
       </c>
@@ -12846,7 +12845,7 @@
         <v>185.11594086400001</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="108" t="s">
         <v>472</v>
       </c>
@@ -12891,24 +12890,23 @@
         <v>0.72661280000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="157" t="s">
+    <row r="30" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="161" t="s">
         <v>513</v>
       </c>
-      <c r="B30" s="157"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="157"/>
-      <c r="F30" s="157"/>
-      <c r="G30" s="157"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="157"/>
-      <c r="J30" s="157"/>
-      <c r="K30" s="157"/>
-      <c r="L30" s="157"/>
-      <c r="M30" s="157"/>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="161"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="161"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
         <v>61</v>
       </c>
@@ -12953,7 +12951,7 @@
         <v>2098.1519608603717</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="s">
         <v>476</v>
       </c>
@@ -13180,9 +13178,9 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A14:L14"/>
@@ -13215,54 +13213,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="207" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="160" t="s">
         <v>514</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="162" t="s">
         <v>515</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
@@ -13303,20 +13301,20 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="205" t="s">
+      <c r="A6" s="209" t="s">
         <v>516</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
-      <c r="L6" s="205"/>
+      <c r="B6" s="209"/>
+      <c r="C6" s="209"/>
+      <c r="D6" s="209"/>
+      <c r="E6" s="209"/>
+      <c r="F6" s="209"/>
+      <c r="G6" s="209"/>
+      <c r="H6" s="209"/>
+      <c r="I6" s="209"/>
+      <c r="J6" s="209"/>
+      <c r="K6" s="209"/>
+      <c r="L6" s="209"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="105" t="s">
@@ -13586,20 +13584,20 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="205" t="s">
+      <c r="A14" s="209" t="s">
         <v>517</v>
       </c>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
-      <c r="F14" s="205"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="205"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="205"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+      <c r="F14" s="209"/>
+      <c r="G14" s="209"/>
+      <c r="H14" s="209"/>
+      <c r="I14" s="209"/>
+      <c r="J14" s="209"/>
+      <c r="K14" s="209"/>
+      <c r="L14" s="209"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
@@ -13869,20 +13867,20 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="205" t="s">
+      <c r="A22" s="209" t="s">
         <v>518</v>
       </c>
-      <c r="B22" s="205"/>
-      <c r="C22" s="205"/>
-      <c r="D22" s="205"/>
-      <c r="E22" s="205"/>
-      <c r="F22" s="205"/>
-      <c r="G22" s="205"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="205"/>
-      <c r="K22" s="205"/>
-      <c r="L22" s="205"/>
+      <c r="B22" s="209"/>
+      <c r="C22" s="209"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="209"/>
+      <c r="F22" s="209"/>
+      <c r="G22" s="209"/>
+      <c r="H22" s="209"/>
+      <c r="I22" s="209"/>
+      <c r="J22" s="209"/>
+      <c r="K22" s="209"/>
+      <c r="L22" s="209"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="105" t="s">
@@ -14152,20 +14150,20 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="157" t="s">
+      <c r="A30" s="161" t="s">
         <v>519</v>
       </c>
-      <c r="B30" s="157"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="157"/>
-      <c r="F30" s="157"/>
-      <c r="G30" s="157"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="157"/>
-      <c r="J30" s="157"/>
-      <c r="K30" s="157"/>
-      <c r="L30" s="157"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="161"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
@@ -14474,54 +14472,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="207" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="160" t="s">
         <v>520</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="162" t="s">
         <v>521</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
@@ -14562,20 +14560,20 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="206" t="s">
+      <c r="A6" s="210" t="s">
         <v>522</v>
       </c>
-      <c r="B6" s="206"/>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="206"/>
-      <c r="H6" s="206"/>
-      <c r="I6" s="206"/>
-      <c r="J6" s="206"/>
-      <c r="K6" s="206"/>
-      <c r="L6" s="206"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="210"/>
+      <c r="K6" s="210"/>
+      <c r="L6" s="210"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="105" t="s">
@@ -14845,20 +14843,20 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206" t="s">
+      <c r="A14" s="210" t="s">
         <v>523</v>
       </c>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="206"/>
-      <c r="G14" s="206"/>
-      <c r="H14" s="206"/>
-      <c r="I14" s="206"/>
-      <c r="J14" s="206"/>
-      <c r="K14" s="206"/>
-      <c r="L14" s="206"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
+      <c r="I14" s="210"/>
+      <c r="J14" s="210"/>
+      <c r="K14" s="210"/>
+      <c r="L14" s="210"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
@@ -15128,20 +15126,20 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="206" t="s">
+      <c r="A22" s="210" t="s">
         <v>524</v>
       </c>
-      <c r="B22" s="206"/>
-      <c r="C22" s="206"/>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
-      <c r="G22" s="206"/>
-      <c r="H22" s="206"/>
-      <c r="I22" s="206"/>
-      <c r="J22" s="206"/>
-      <c r="K22" s="206"/>
-      <c r="L22" s="206"/>
+      <c r="B22" s="210"/>
+      <c r="C22" s="210"/>
+      <c r="D22" s="210"/>
+      <c r="E22" s="210"/>
+      <c r="F22" s="210"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="210"/>
+      <c r="I22" s="210"/>
+      <c r="J22" s="210"/>
+      <c r="K22" s="210"/>
+      <c r="L22" s="210"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="105" t="s">
@@ -15411,20 +15409,20 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="157" t="s">
+      <c r="A30" s="161" t="s">
         <v>525</v>
       </c>
-      <c r="B30" s="157"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="157"/>
-      <c r="F30" s="157"/>
-      <c r="G30" s="157"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="157"/>
-      <c r="J30" s="157"/>
-      <c r="K30" s="157"/>
-      <c r="L30" s="157"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="161"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
@@ -15732,36 +15730,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="207" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="160" t="s">
         <v>527</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -15807,20 +15805,20 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="161" t="s">
         <v>530</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="74" t="s">
@@ -16157,20 +16155,20 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="161" t="s">
         <v>533</v>
       </c>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="157"/>
-      <c r="F14" s="157"/>
-      <c r="G14" s="157"/>
-      <c r="H14" s="157"/>
-      <c r="I14" s="157"/>
-      <c r="J14" s="157"/>
-      <c r="K14" s="157"/>
-      <c r="L14" s="157"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="161"/>
+      <c r="G14" s="161"/>
+      <c r="H14" s="161"/>
+      <c r="I14" s="161"/>
+      <c r="J14" s="161"/>
+      <c r="K14" s="161"/>
+      <c r="L14" s="161"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
@@ -16443,20 +16441,20 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="157" t="s">
+      <c r="A22" s="161" t="s">
         <v>540</v>
       </c>
-      <c r="B22" s="157"/>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="157"/>
-      <c r="I22" s="157"/>
-      <c r="J22" s="157"/>
-      <c r="K22" s="157"/>
-      <c r="L22" s="157"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="161"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="74" t="s">
@@ -16792,20 +16790,20 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="157" t="s">
+      <c r="A31" s="161" t="s">
         <v>543</v>
       </c>
-      <c r="B31" s="157"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="157"/>
+      <c r="B31" s="161"/>
+      <c r="C31" s="161"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="161"/>
+      <c r="L31" s="161"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="s">
@@ -16942,36 +16940,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>547</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
     </row>
     <row r="3" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>548</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
-      <c r="J3" s="207"/>
-      <c r="K3" s="207"/>
-      <c r="L3" s="207"/>
-      <c r="M3" s="207"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="211"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="M3" s="211"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -17012,20 +17010,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="161" t="s">
         <v>550</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="105" t="s">
@@ -17262,20 +17260,20 @@
       </c>
     </row>
     <row r="12" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="157" t="s">
+      <c r="B12" s="161" t="s">
         <v>557</v>
       </c>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="157"/>
-      <c r="H12" s="157"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="157"/>
-      <c r="K12" s="157"/>
-      <c r="L12" s="157"/>
-      <c r="M12" s="157"/>
+      <c r="C12" s="161"/>
+      <c r="D12" s="161"/>
+      <c r="E12" s="161"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="161"/>
+      <c r="H12" s="161"/>
+      <c r="I12" s="161"/>
+      <c r="J12" s="161"/>
+      <c r="K12" s="161"/>
+      <c r="L12" s="161"/>
+      <c r="M12" s="161"/>
     </row>
     <row r="13" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="105" t="s">
@@ -17512,20 +17510,20 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="157" t="s">
+      <c r="B19" s="161" t="s">
         <v>564</v>
       </c>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="157"/>
-      <c r="G19" s="157"/>
-      <c r="H19" s="157"/>
-      <c r="I19" s="157"/>
-      <c r="J19" s="157"/>
-      <c r="K19" s="157"/>
-      <c r="L19" s="157"/>
-      <c r="M19" s="157"/>
+      <c r="C19" s="161"/>
+      <c r="D19" s="161"/>
+      <c r="E19" s="161"/>
+      <c r="F19" s="161"/>
+      <c r="G19" s="161"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="161"/>
+      <c r="J19" s="161"/>
+      <c r="K19" s="161"/>
+      <c r="L19" s="161"/>
+      <c r="M19" s="161"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="105" t="s">
@@ -17783,20 +17781,20 @@
       </c>
     </row>
     <row r="28" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="157" t="s">
+      <c r="B28" s="161" t="s">
         <v>572</v>
       </c>
-      <c r="C28" s="157"/>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="157"/>
-      <c r="G28" s="157"/>
-      <c r="H28" s="157"/>
-      <c r="I28" s="157"/>
-      <c r="J28" s="157"/>
-      <c r="K28" s="157"/>
-      <c r="L28" s="157"/>
-      <c r="M28" s="157"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="161"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="161"/>
+      <c r="K28" s="161"/>
+      <c r="L28" s="161"/>
+      <c r="M28" s="161"/>
     </row>
     <row r="29" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="105" t="s">
@@ -18114,20 +18112,20 @@
       </c>
     </row>
     <row r="37" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="157" t="s">
+      <c r="B37" s="161" t="s">
         <v>580</v>
       </c>
-      <c r="C37" s="157"/>
-      <c r="D37" s="157"/>
-      <c r="E37" s="157"/>
-      <c r="F37" s="157"/>
-      <c r="G37" s="157"/>
-      <c r="H37" s="157"/>
-      <c r="I37" s="157"/>
-      <c r="J37" s="157"/>
-      <c r="K37" s="157"/>
-      <c r="L37" s="157"/>
-      <c r="M37" s="157"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="161"/>
+      <c r="E37" s="161"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="161"/>
+      <c r="K37" s="161"/>
+      <c r="L37" s="161"/>
+      <c r="M37" s="161"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="s">
@@ -18265,20 +18263,20 @@
       </c>
     </row>
     <row r="42" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="157" t="s">
+      <c r="B42" s="161" t="s">
         <v>584</v>
       </c>
-      <c r="C42" s="157"/>
-      <c r="D42" s="157"/>
-      <c r="E42" s="157"/>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
-      <c r="I42" s="157"/>
-      <c r="J42" s="157"/>
-      <c r="K42" s="157"/>
-      <c r="L42" s="157"/>
-      <c r="M42" s="157"/>
+      <c r="C42" s="161"/>
+      <c r="D42" s="161"/>
+      <c r="E42" s="161"/>
+      <c r="F42" s="161"/>
+      <c r="G42" s="161"/>
+      <c r="H42" s="161"/>
+      <c r="I42" s="161"/>
+      <c r="J42" s="161"/>
+      <c r="K42" s="161"/>
+      <c r="L42" s="161"/>
+      <c r="M42" s="161"/>
     </row>
     <row r="43" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="105" t="s">
@@ -18596,20 +18594,20 @@
       </c>
     </row>
     <row r="51" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="157" t="s">
+      <c r="B51" s="161" t="s">
         <v>590</v>
       </c>
-      <c r="C51" s="157"/>
-      <c r="D51" s="157"/>
-      <c r="E51" s="157"/>
-      <c r="F51" s="157"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="157"/>
-      <c r="I51" s="157"/>
-      <c r="J51" s="157"/>
-      <c r="K51" s="157"/>
-      <c r="L51" s="157"/>
-      <c r="M51" s="157"/>
+      <c r="C51" s="161"/>
+      <c r="D51" s="161"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="161"/>
+      <c r="G51" s="161"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="161"/>
+      <c r="K51" s="161"/>
+      <c r="L51" s="161"/>
+      <c r="M51" s="161"/>
     </row>
     <row r="52" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="105" t="s">
@@ -18882,20 +18880,20 @@
       </c>
     </row>
     <row r="59" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="157" t="s">
+      <c r="B59" s="161" t="s">
         <v>597</v>
       </c>
-      <c r="C59" s="157"/>
-      <c r="D59" s="157"/>
-      <c r="E59" s="157"/>
-      <c r="F59" s="157"/>
-      <c r="G59" s="157"/>
-      <c r="H59" s="157"/>
-      <c r="I59" s="157"/>
-      <c r="J59" s="157"/>
-      <c r="K59" s="157"/>
-      <c r="L59" s="157"/>
-      <c r="M59" s="157"/>
+      <c r="C59" s="161"/>
+      <c r="D59" s="161"/>
+      <c r="E59" s="161"/>
+      <c r="F59" s="161"/>
+      <c r="G59" s="161"/>
+      <c r="H59" s="161"/>
+      <c r="I59" s="161"/>
+      <c r="J59" s="161"/>
+      <c r="K59" s="161"/>
+      <c r="L59" s="161"/>
+      <c r="M59" s="161"/>
     </row>
     <row r="60" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="105" t="s">
@@ -19123,132 +19121,132 @@
       </c>
     </row>
     <row r="66" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="157" t="s">
+      <c r="B66" s="161" t="s">
         <v>603</v>
       </c>
-      <c r="C66" s="157"/>
-      <c r="D66" s="157"/>
-      <c r="E66" s="157"/>
-      <c r="F66" s="157"/>
-      <c r="G66" s="157"/>
-      <c r="H66" s="157"/>
-      <c r="I66" s="157"/>
-      <c r="J66" s="157"/>
-      <c r="K66" s="157"/>
-      <c r="L66" s="157"/>
-      <c r="M66" s="157"/>
+      <c r="C66" s="161"/>
+      <c r="D66" s="161"/>
+      <c r="E66" s="161"/>
+      <c r="F66" s="161"/>
+      <c r="G66" s="161"/>
+      <c r="H66" s="161"/>
+      <c r="I66" s="161"/>
+      <c r="J66" s="161"/>
+      <c r="K66" s="161"/>
+      <c r="L66" s="161"/>
+      <c r="M66" s="161"/>
     </row>
     <row r="67" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="207" t="s">
+      <c r="B67" s="211" t="s">
         <v>604</v>
       </c>
-      <c r="C67" s="207"/>
-      <c r="D67" s="207"/>
-      <c r="E67" s="207"/>
-      <c r="F67" s="207"/>
-      <c r="G67" s="207"/>
-      <c r="H67" s="207"/>
-      <c r="I67" s="207"/>
-      <c r="J67" s="207"/>
-      <c r="K67" s="207"/>
-      <c r="L67" s="207"/>
-      <c r="M67" s="207"/>
+      <c r="C67" s="211"/>
+      <c r="D67" s="211"/>
+      <c r="E67" s="211"/>
+      <c r="F67" s="211"/>
+      <c r="G67" s="211"/>
+      <c r="H67" s="211"/>
+      <c r="I67" s="211"/>
+      <c r="J67" s="211"/>
+      <c r="K67" s="211"/>
+      <c r="L67" s="211"/>
+      <c r="M67" s="211"/>
     </row>
     <row r="68" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="207" t="s">
+      <c r="B68" s="211" t="s">
         <v>605</v>
       </c>
-      <c r="C68" s="207"/>
-      <c r="D68" s="207"/>
-      <c r="E68" s="207"/>
-      <c r="F68" s="207"/>
-      <c r="G68" s="207"/>
-      <c r="H68" s="207"/>
-      <c r="I68" s="207"/>
-      <c r="J68" s="207"/>
-      <c r="K68" s="207"/>
-      <c r="L68" s="207"/>
-      <c r="M68" s="207"/>
+      <c r="C68" s="211"/>
+      <c r="D68" s="211"/>
+      <c r="E68" s="211"/>
+      <c r="F68" s="211"/>
+      <c r="G68" s="211"/>
+      <c r="H68" s="211"/>
+      <c r="I68" s="211"/>
+      <c r="J68" s="211"/>
+      <c r="K68" s="211"/>
+      <c r="L68" s="211"/>
+      <c r="M68" s="211"/>
     </row>
     <row r="69" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="207" t="s">
+      <c r="B69" s="211" t="s">
         <v>606</v>
       </c>
-      <c r="C69" s="207"/>
-      <c r="D69" s="207"/>
-      <c r="E69" s="207"/>
-      <c r="F69" s="207"/>
-      <c r="G69" s="207"/>
-      <c r="H69" s="207"/>
-      <c r="I69" s="207"/>
-      <c r="J69" s="207"/>
-      <c r="K69" s="207"/>
-      <c r="L69" s="207"/>
-      <c r="M69" s="207"/>
+      <c r="C69" s="211"/>
+      <c r="D69" s="211"/>
+      <c r="E69" s="211"/>
+      <c r="F69" s="211"/>
+      <c r="G69" s="211"/>
+      <c r="H69" s="211"/>
+      <c r="I69" s="211"/>
+      <c r="J69" s="211"/>
+      <c r="K69" s="211"/>
+      <c r="L69" s="211"/>
+      <c r="M69" s="211"/>
     </row>
     <row r="70" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="207" t="s">
+      <c r="B70" s="211" t="s">
         <v>607</v>
       </c>
-      <c r="C70" s="207"/>
-      <c r="D70" s="207"/>
-      <c r="E70" s="207"/>
-      <c r="F70" s="207"/>
-      <c r="G70" s="207"/>
-      <c r="H70" s="207"/>
-      <c r="I70" s="207"/>
-      <c r="J70" s="207"/>
-      <c r="K70" s="207"/>
-      <c r="L70" s="207"/>
-      <c r="M70" s="207"/>
+      <c r="C70" s="211"/>
+      <c r="D70" s="211"/>
+      <c r="E70" s="211"/>
+      <c r="F70" s="211"/>
+      <c r="G70" s="211"/>
+      <c r="H70" s="211"/>
+      <c r="I70" s="211"/>
+      <c r="J70" s="211"/>
+      <c r="K70" s="211"/>
+      <c r="L70" s="211"/>
+      <c r="M70" s="211"/>
     </row>
     <row r="71" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="207" t="s">
+      <c r="B71" s="211" t="s">
         <v>608</v>
       </c>
-      <c r="C71" s="207"/>
-      <c r="D71" s="207"/>
-      <c r="E71" s="207"/>
-      <c r="F71" s="207"/>
-      <c r="G71" s="207"/>
-      <c r="H71" s="207"/>
-      <c r="I71" s="207"/>
-      <c r="J71" s="207"/>
-      <c r="K71" s="207"/>
-      <c r="L71" s="207"/>
-      <c r="M71" s="207"/>
+      <c r="C71" s="211"/>
+      <c r="D71" s="211"/>
+      <c r="E71" s="211"/>
+      <c r="F71" s="211"/>
+      <c r="G71" s="211"/>
+      <c r="H71" s="211"/>
+      <c r="I71" s="211"/>
+      <c r="J71" s="211"/>
+      <c r="K71" s="211"/>
+      <c r="L71" s="211"/>
+      <c r="M71" s="211"/>
     </row>
     <row r="72" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="207" t="s">
+      <c r="B72" s="211" t="s">
         <v>609</v>
       </c>
-      <c r="C72" s="207"/>
-      <c r="D72" s="207"/>
-      <c r="E72" s="207"/>
-      <c r="F72" s="207"/>
-      <c r="G72" s="207"/>
-      <c r="H72" s="207"/>
-      <c r="I72" s="207"/>
-      <c r="J72" s="207"/>
-      <c r="K72" s="207"/>
-      <c r="L72" s="207"/>
-      <c r="M72" s="207"/>
+      <c r="C72" s="211"/>
+      <c r="D72" s="211"/>
+      <c r="E72" s="211"/>
+      <c r="F72" s="211"/>
+      <c r="G72" s="211"/>
+      <c r="H72" s="211"/>
+      <c r="I72" s="211"/>
+      <c r="J72" s="211"/>
+      <c r="K72" s="211"/>
+      <c r="L72" s="211"/>
+      <c r="M72" s="211"/>
     </row>
     <row r="73" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="207" t="s">
+      <c r="B73" s="211" t="s">
         <v>610</v>
       </c>
-      <c r="C73" s="207"/>
-      <c r="D73" s="207"/>
-      <c r="E73" s="207"/>
-      <c r="F73" s="207"/>
-      <c r="G73" s="207"/>
-      <c r="H73" s="207"/>
-      <c r="I73" s="207"/>
-      <c r="J73" s="207"/>
-      <c r="K73" s="207"/>
-      <c r="L73" s="207"/>
-      <c r="M73" s="207"/>
+      <c r="C73" s="211"/>
+      <c r="D73" s="211"/>
+      <c r="E73" s="211"/>
+      <c r="F73" s="211"/>
+      <c r="G73" s="211"/>
+      <c r="H73" s="211"/>
+      <c r="I73" s="211"/>
+      <c r="J73" s="211"/>
+      <c r="K73" s="211"/>
+      <c r="L73" s="211"/>
+      <c r="M73" s="211"/>
     </row>
     <row r="74" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
@@ -20081,12 +20079,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B28:M28"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="B19:M19"/>
     <mergeCell ref="B73:M73"/>
     <mergeCell ref="B37:M37"/>
     <mergeCell ref="B42:M42"/>
@@ -20099,6 +20091,12 @@
     <mergeCell ref="B70:M70"/>
     <mergeCell ref="B71:M71"/>
     <mergeCell ref="B72:M72"/>
+    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="B19:M19"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20125,20 +20123,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="204" t="s">
         <v>638</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
@@ -21307,20 +21305,20 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="198" t="s">
+      <c r="A35" s="202" t="s">
         <v>670</v>
       </c>
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="198"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="198"/>
-      <c r="K35" s="198"/>
-      <c r="L35" s="198"/>
+      <c r="B35" s="202"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="202"/>
+      <c r="F35" s="202"/>
+      <c r="G35" s="202"/>
+      <c r="H35" s="202"/>
+      <c r="I35" s="202"/>
+      <c r="J35" s="202"/>
+      <c r="K35" s="202"/>
+      <c r="L35" s="202"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="105" t="s">
@@ -22910,20 +22908,20 @@
       </c>
     </row>
     <row r="71" spans="1:12" s="29" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="159" t="s">
+      <c r="A71" s="169" t="s">
         <v>709</v>
       </c>
-      <c r="B71" s="159"/>
-      <c r="C71" s="159"/>
-      <c r="D71" s="159"/>
-      <c r="E71" s="159"/>
-      <c r="F71" s="159"/>
-      <c r="G71" s="159"/>
-      <c r="H71" s="159"/>
-      <c r="I71" s="159"/>
-      <c r="J71" s="159"/>
-      <c r="K71" s="159"/>
-      <c r="L71" s="159"/>
+      <c r="B71" s="169"/>
+      <c r="C71" s="169"/>
+      <c r="D71" s="169"/>
+      <c r="E71" s="169"/>
+      <c r="F71" s="169"/>
+      <c r="G71" s="169"/>
+      <c r="H71" s="169"/>
+      <c r="I71" s="169"/>
+      <c r="J71" s="169"/>
+      <c r="K71" s="169"/>
+      <c r="L71" s="169"/>
     </row>
     <row r="75" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="139"/>
@@ -22961,20 +22959,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>710</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -23252,20 +23250,20 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="161" t="s">
         <v>721</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="161"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="161"/>
+      <c r="L11" s="161"/>
+      <c r="M11" s="161"/>
     </row>
     <row r="12" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B12" s="140" t="s">
@@ -23592,83 +23590,83 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="166" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="165" t="s">
+      <c r="A3" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="165"/>
-      <c r="C3" s="165" t="s">
+      <c r="B3" s="167"/>
+      <c r="C3" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165" t="s">
+      <c r="D3" s="167"/>
+      <c r="E3" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="165"/>
-      <c r="G3" s="165" t="s">
+      <c r="F3" s="167"/>
+      <c r="G3" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="165"/>
-      <c r="I3" s="165" t="s">
+      <c r="H3" s="167"/>
+      <c r="I3" s="167" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="165"/>
+      <c r="J3" s="167"/>
     </row>
     <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="160">
+      <c r="A4" s="170">
         <f>'P&amp;L'!L5</f>
         <v>5054.7779683549852</v>
       </c>
-      <c r="B4" s="160"/>
-      <c r="C4" s="161" t="str">
+      <c r="B4" s="170"/>
+      <c r="C4" s="171" t="str">
         <f>"₹ "&amp;TEXT('P&amp;L'!L16,"#,##0.0")&amp;" Cr ("&amp;TEXT(IFERROR('P&amp;L'!L16/'P&amp;L'!L5,0),"0.0%")&amp;")"</f>
         <v>₹ 2,346.8 Cr (46.4%)</v>
       </c>
-      <c r="D4" s="161"/>
-      <c r="E4" s="160">
+      <c r="D4" s="171"/>
+      <c r="E4" s="170">
         <f ca="1">SUM(CashFlow!C27:L27)</f>
         <v>4797.1503952717703</v>
       </c>
-      <c r="F4" s="160"/>
-      <c r="G4" s="162">
+      <c r="F4" s="170"/>
+      <c r="G4" s="172">
         <f ca="1">IFERROR(IRR(CashFlow!C27:L27),0)</f>
         <v>0.32203596861715522</v>
       </c>
-      <c r="H4" s="162"/>
-      <c r="I4" s="160">
+      <c r="H4" s="172"/>
+      <c r="I4" s="170">
         <f ca="1">NPV(Assumptions!$C$7,CashFlow!C27:L27)</f>
         <v>755.20195796986445</v>
       </c>
-      <c r="J4" s="160"/>
+      <c r="J4" s="170"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="163" t="s">
+      <c r="A6" s="160" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="163"/>
-      <c r="C6" s="163"/>
-      <c r="D6" s="163"/>
-      <c r="E6" s="163"/>
-      <c r="F6" s="163"/>
-      <c r="G6" s="163"/>
-      <c r="H6" s="163"/>
-      <c r="I6" s="163"/>
-      <c r="J6" s="163"/>
-      <c r="K6" s="163"/>
+      <c r="B6" s="160"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
@@ -24831,19 +24829,19 @@
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="157" t="s">
+      <c r="A35" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="157"/>
-      <c r="C35" s="157"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="157"/>
-      <c r="F35" s="157"/>
-      <c r="G35" s="157"/>
-      <c r="H35" s="157"/>
-      <c r="I35" s="157"/>
-      <c r="J35" s="157"/>
-      <c r="K35" s="157"/>
+      <c r="B35" s="161"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="161"/>
+      <c r="E35" s="161"/>
+      <c r="F35" s="161"/>
+      <c r="G35" s="161"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="161"/>
+      <c r="J35" s="161"/>
+      <c r="K35" s="161"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
@@ -24954,19 +24952,19 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="158" t="s">
+      <c r="A49" s="168" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="158"/>
-      <c r="C49" s="158"/>
-      <c r="D49" s="158"/>
-      <c r="E49" s="158"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="158"/>
+      <c r="B49" s="168"/>
+      <c r="C49" s="168"/>
+      <c r="D49" s="168"/>
+      <c r="E49" s="168"/>
+      <c r="F49" s="168"/>
+      <c r="G49" s="168"/>
+      <c r="H49" s="168"/>
+      <c r="I49" s="168"/>
+      <c r="J49" s="168"/>
+      <c r="K49" s="168"/>
     </row>
     <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
@@ -25274,27 +25272,21 @@
       <c r="A65" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="B65" s="159" t="s">
+      <c r="B65" s="169" t="s">
         <v>115</v>
       </c>
-      <c r="C65" s="159"/>
-      <c r="D65" s="159"/>
-      <c r="E65" s="159"/>
-      <c r="F65" s="159"/>
-      <c r="G65" s="159"/>
-      <c r="H65" s="159"/>
-      <c r="I65" s="159"/>
-      <c r="J65" s="159"/>
-      <c r="K65" s="159"/>
+      <c r="C65" s="169"/>
+      <c r="D65" s="169"/>
+      <c r="E65" s="169"/>
+      <c r="F65" s="169"/>
+      <c r="G65" s="169"/>
+      <c r="H65" s="169"/>
+      <c r="I65" s="169"/>
+      <c r="J65" s="169"/>
+      <c r="K65" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A49:K49"/>
     <mergeCell ref="B65:K65"/>
@@ -25304,6 +25296,12 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25336,20 +25334,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>733</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -25390,20 +25388,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="161" t="s">
         <v>736</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="105" t="s">
@@ -26000,20 +25998,20 @@
       </c>
     </row>
     <row r="23" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="161" t="s">
         <v>753</v>
       </c>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="157"/>
-      <c r="M23" s="157"/>
+      <c r="C23" s="161"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="161"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="161"/>
+      <c r="K23" s="161"/>
+      <c r="L23" s="161"/>
+      <c r="M23" s="161"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="108" t="s">
@@ -26768,20 +26766,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>770</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -26820,20 +26818,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="161" t="s">
         <v>771</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="105" t="s">
@@ -27546,19 +27544,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>790</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -29128,19 +29126,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>820</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -29178,19 +29176,19 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="161" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
     </row>
     <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -29643,19 +29641,19 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="157" t="s">
+      <c r="B16" s="161" t="s">
         <v>831</v>
       </c>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
-      <c r="F16" s="157"/>
-      <c r="G16" s="157"/>
-      <c r="H16" s="157"/>
-      <c r="I16" s="157"/>
-      <c r="J16" s="157"/>
-      <c r="K16" s="157"/>
-      <c r="L16" s="157"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="161"/>
     </row>
     <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
@@ -29793,19 +29791,19 @@
       </c>
     </row>
     <row r="21" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="157" t="s">
+      <c r="B21" s="161" t="s">
         <v>835</v>
       </c>
-      <c r="C21" s="157"/>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
-      <c r="G21" s="157"/>
-      <c r="H21" s="157"/>
-      <c r="I21" s="157"/>
-      <c r="J21" s="157"/>
-      <c r="K21" s="157"/>
-      <c r="L21" s="157"/>
+      <c r="C21" s="161"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="161"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161"/>
+      <c r="L21" s="161"/>
     </row>
     <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="45" t="s">
@@ -29943,19 +29941,19 @@
       </c>
     </row>
     <row r="26" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="157" t="s">
+      <c r="B26" s="161" t="s">
         <v>838</v>
       </c>
-      <c r="C26" s="157"/>
-      <c r="D26" s="157"/>
-      <c r="E26" s="157"/>
-      <c r="F26" s="157"/>
-      <c r="G26" s="157"/>
-      <c r="H26" s="157"/>
-      <c r="I26" s="157"/>
-      <c r="J26" s="157"/>
-      <c r="K26" s="157"/>
-      <c r="L26" s="157"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="161"/>
+      <c r="F26" s="161"/>
+      <c r="G26" s="161"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="161"/>
+      <c r="J26" s="161"/>
+      <c r="K26" s="161"/>
+      <c r="L26" s="161"/>
     </row>
     <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="44" t="s">
@@ -30396,34 +30394,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>848</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="3" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>849</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
-      <c r="J3" s="207"/>
-      <c r="K3" s="207"/>
-      <c r="L3" s="207"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="211"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
     </row>
     <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -30461,19 +30459,19 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="161" t="s">
         <v>850</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
     </row>
     <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -30971,19 +30969,19 @@
       </c>
     </row>
     <row r="18" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="157" t="s">
+      <c r="B18" s="161" t="s">
         <v>861</v>
       </c>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="157"/>
-      <c r="F18" s="157"/>
-      <c r="G18" s="157"/>
-      <c r="H18" s="157"/>
-      <c r="I18" s="157"/>
-      <c r="J18" s="157"/>
-      <c r="K18" s="157"/>
-      <c r="L18" s="157"/>
+      <c r="C18" s="161"/>
+      <c r="D18" s="161"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="161"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="161"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="161"/>
     </row>
     <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
@@ -31166,19 +31164,19 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="157" t="s">
+      <c r="B24" s="161" t="s">
         <v>866</v>
       </c>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="157"/>
-      <c r="G24" s="157"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="157"/>
-      <c r="J24" s="157"/>
-      <c r="K24" s="157"/>
-      <c r="L24" s="157"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="161"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="161"/>
+      <c r="J24" s="161"/>
+      <c r="K24" s="161"/>
+      <c r="L24" s="161"/>
     </row>
     <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
@@ -31361,19 +31359,19 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="157" t="s">
+      <c r="B31" s="161" t="s">
         <v>871</v>
       </c>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="157"/>
+      <c r="C31" s="161"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="161"/>
+      <c r="L31" s="161"/>
     </row>
     <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
@@ -31815,20 +31813,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="160" t="s">
         <v>881</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -31869,20 +31867,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="161" t="s">
         <v>884</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
     </row>
     <row r="6" spans="2:13" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
@@ -32044,7 +32042,7 @@
       </c>
     </row>
     <row r="10" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="213" t="s">
+      <c r="B10" s="159" t="s">
         <v>947</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -32082,20 +32080,20 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="161" t="s">
         <v>892</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="161"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="161"/>
+      <c r="L11" s="161"/>
+      <c r="M11" s="161"/>
     </row>
     <row r="12" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
@@ -32352,20 +32350,20 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="157" t="s">
+      <c r="B19" s="161" t="s">
         <v>899</v>
       </c>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="157"/>
-      <c r="G19" s="157"/>
-      <c r="H19" s="157"/>
-      <c r="I19" s="157"/>
-      <c r="J19" s="157"/>
-      <c r="K19" s="157"/>
-      <c r="L19" s="157"/>
-      <c r="M19" s="157"/>
+      <c r="C19" s="161"/>
+      <c r="D19" s="161"/>
+      <c r="E19" s="161"/>
+      <c r="F19" s="161"/>
+      <c r="G19" s="161"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="161"/>
+      <c r="J19" s="161"/>
+      <c r="K19" s="161"/>
+      <c r="L19" s="161"/>
+      <c r="M19" s="161"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="45" t="s">
@@ -32690,14 +32688,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="212" t="s">
         <v>909</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
@@ -32708,14 +32706,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="161" t="s">
         <v>911</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
     </row>
     <row r="6" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
@@ -32913,24 +32911,24 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="209" t="s">
+      <c r="A14" s="213" t="s">
         <v>918</v>
       </c>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
-      <c r="F14" s="209"/>
+      <c r="B14" s="213"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="213"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="161" t="s">
         <v>919</v>
       </c>
-      <c r="B15" s="157"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="157"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="161"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -32996,14 +32994,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="157" t="s">
+      <c r="A24" s="161" t="s">
         <v>927</v>
       </c>
-      <c r="B24" s="157"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="157"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45" t="s">
@@ -33024,14 +33022,14 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="157" t="s">
+      <c r="A28" s="161" t="s">
         <v>930</v>
       </c>
-      <c r="B28" s="157"/>
-      <c r="C28" s="157"/>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="157"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="161"/>
+      <c r="F28" s="161"/>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
@@ -33166,10 +33164,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="169" t="s">
+      <c r="B1" s="173" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="169"/>
+      <c r="C1" s="173"/>
     </row>
     <row r="2" spans="2:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
@@ -33223,7 +33221,7 @@
       <c r="B8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="212" t="s">
+      <c r="C8" s="157" t="s">
         <v>946</v>
       </c>
     </row>
@@ -33288,16 +33286,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="163" t="s">
+      <c r="B1" s="160" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="163"/>
-      <c r="H1" s="163"/>
-      <c r="I1" s="163"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
     </row>
     <row r="3" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
@@ -33749,72 +33747,72 @@
       </c>
     </row>
     <row r="21" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="157" t="s">
+      <c r="B21" s="161" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="157"/>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
-      <c r="G21" s="157"/>
-      <c r="H21" s="157"/>
-      <c r="I21" s="157"/>
+      <c r="C21" s="161"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="161"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
     </row>
     <row r="22" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C22" s="166" t="s">
+      <c r="C22" s="162" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
     </row>
     <row r="23" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="166" t="s">
+      <c r="C23" s="162" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="166"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
     </row>
     <row r="24" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="166" t="s">
+      <c r="C24" s="162" t="s">
         <v>168</v>
       </c>
-      <c r="D24" s="166"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="166"/>
-      <c r="G24" s="166"/>
-      <c r="H24" s="166"/>
-      <c r="I24" s="166"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
     </row>
     <row r="25" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C25" s="166" t="s">
+      <c r="C25" s="162" t="s">
         <v>170</v>
       </c>
-      <c r="D25" s="166"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="166"/>
-      <c r="I25" s="166"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -33862,20 +33860,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="160" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -34438,20 +34436,20 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="157" t="s">
+      <c r="A20" s="161" t="s">
         <v>206</v>
       </c>
-      <c r="B20" s="157"/>
-      <c r="C20" s="157"/>
-      <c r="D20" s="157"/>
-      <c r="E20" s="157"/>
-      <c r="F20" s="157"/>
-      <c r="G20" s="157"/>
-      <c r="H20" s="157"/>
-      <c r="I20" s="157"/>
-      <c r="J20" s="157"/>
-      <c r="K20" s="157"/>
-      <c r="L20" s="157"/>
+      <c r="B20" s="161"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="161"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="161"/>
     </row>
     <row r="21" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -34515,20 +34513,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="160" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -34569,20 +34567,20 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="161" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -34868,20 +34866,20 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="161" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="157"/>
-      <c r="F14" s="157"/>
-      <c r="G14" s="157"/>
-      <c r="H14" s="157"/>
-      <c r="I14" s="157"/>
-      <c r="J14" s="157"/>
-      <c r="K14" s="157"/>
-      <c r="L14" s="157"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="161"/>
+      <c r="G14" s="161"/>
+      <c r="H14" s="161"/>
+      <c r="I14" s="161"/>
+      <c r="J14" s="161"/>
+      <c r="K14" s="161"/>
+      <c r="L14" s="161"/>
     </row>
     <row r="15" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -35074,20 +35072,20 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="157" t="s">
+      <c r="A20" s="161" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="157"/>
-      <c r="C20" s="157"/>
-      <c r="D20" s="157"/>
-      <c r="E20" s="157"/>
-      <c r="F20" s="157"/>
-      <c r="G20" s="157"/>
-      <c r="H20" s="157"/>
-      <c r="I20" s="157"/>
-      <c r="J20" s="157"/>
-      <c r="K20" s="157"/>
-      <c r="L20" s="157"/>
+      <c r="B20" s="161"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="161"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="161"/>
     </row>
     <row r="21" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45" t="s">
@@ -35347,38 +35345,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="174" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
-      <c r="L2" s="172"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
+      <c r="K2" s="175"/>
+      <c r="L2" s="176"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="177" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="174"/>
-      <c r="L3" s="175"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="179"/>
     </row>
     <row r="5" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A5" s="52" t="s">
@@ -35728,20 +35726,20 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="176" t="s">
+      <c r="A14" s="180" t="s">
         <v>249</v>
       </c>
-      <c r="B14" s="177"/>
-      <c r="C14" s="177"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
-      <c r="F14" s="177"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="177"/>
-      <c r="I14" s="177"/>
-      <c r="J14" s="177"/>
-      <c r="K14" s="177"/>
-      <c r="L14" s="178"/>
+      <c r="B14" s="181"/>
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="181"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="181"/>
+      <c r="L14" s="182"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="54" t="s">
@@ -35972,20 +35970,20 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="176" t="s">
+      <c r="A23" s="180" t="s">
         <v>252</v>
       </c>
-      <c r="B23" s="177"/>
-      <c r="C23" s="177"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="177"/>
-      <c r="F23" s="177"/>
-      <c r="G23" s="177"/>
-      <c r="H23" s="177"/>
-      <c r="I23" s="177"/>
-      <c r="J23" s="177"/>
-      <c r="K23" s="177"/>
-      <c r="L23" s="178"/>
+      <c r="B23" s="181"/>
+      <c r="C23" s="181"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="181"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="181"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="181"/>
+      <c r="L23" s="182"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="54" t="s">
@@ -36216,20 +36214,20 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="176" t="s">
+      <c r="A32" s="180" t="s">
         <v>254</v>
       </c>
-      <c r="B32" s="177"/>
-      <c r="C32" s="177"/>
-      <c r="D32" s="177"/>
-      <c r="E32" s="177"/>
-      <c r="F32" s="177"/>
-      <c r="G32" s="177"/>
-      <c r="H32" s="177"/>
-      <c r="I32" s="177"/>
-      <c r="J32" s="177"/>
-      <c r="K32" s="177"/>
-      <c r="L32" s="178"/>
+      <c r="B32" s="181"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="181"/>
+      <c r="E32" s="181"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="182"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="54" t="s">
@@ -38572,21 +38570,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="182" t="s">
+      <c r="B2" s="186" t="s">
         <v>297</v>
       </c>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
-      <c r="L2" s="182"/>
-      <c r="M2" s="182"/>
-      <c r="N2" s="182"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
+      <c r="E2" s="186"/>
+      <c r="F2" s="186"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="186"/>
+      <c r="M2" s="186"/>
+      <c r="N2" s="186"/>
     </row>
     <row r="3" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -38756,21 +38754,21 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="161" t="s">
         <v>310</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="157"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="161"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="161"/>
+      <c r="L11" s="161"/>
+      <c r="M11" s="161"/>
+      <c r="N11" s="161"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
@@ -39080,21 +39078,21 @@
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
-      <c r="B20" s="157" t="s">
+      <c r="B20" s="161" t="s">
         <v>311</v>
       </c>
-      <c r="C20" s="157"/>
-      <c r="D20" s="157"/>
-      <c r="E20" s="157"/>
-      <c r="F20" s="157"/>
-      <c r="G20" s="157"/>
-      <c r="H20" s="157"/>
-      <c r="I20" s="157"/>
-      <c r="J20" s="157"/>
-      <c r="K20" s="157"/>
-      <c r="L20" s="157"/>
-      <c r="M20" s="157"/>
-      <c r="N20" s="157"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="161"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="161"/>
+      <c r="M20" s="161"/>
+      <c r="N20" s="161"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
@@ -39956,27 +39954,27 @@
       </c>
     </row>
     <row r="41" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="157" t="s">
+      <c r="B41" s="161" t="s">
         <v>338</v>
       </c>
-      <c r="C41" s="157"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="157"/>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
-      <c r="H41" s="157"/>
-      <c r="I41" s="157"/>
-      <c r="J41" s="157"/>
-      <c r="K41" s="157"/>
-      <c r="L41" s="157"/>
-      <c r="M41" s="157"/>
+      <c r="C41" s="161"/>
+      <c r="D41" s="161"/>
+      <c r="E41" s="161"/>
+      <c r="F41" s="161"/>
+      <c r="G41" s="161"/>
+      <c r="H41" s="161"/>
+      <c r="I41" s="161"/>
+      <c r="J41" s="161"/>
+      <c r="K41" s="161"/>
+      <c r="L41" s="161"/>
+      <c r="M41" s="161"/>
       <c r="N41" s="88"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="183" t="s">
+      <c r="B42" s="187" t="s">
         <v>339</v>
       </c>
-      <c r="C42" s="183"/>
+      <c r="C42" s="187"/>
       <c r="D42" s="36" t="s">
         <v>27</v>
       </c>
@@ -40009,10 +40007,10 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B43" s="179" t="s">
+      <c r="B43" s="183" t="s">
         <v>340</v>
       </c>
-      <c r="C43" s="179"/>
+      <c r="C43" s="183"/>
       <c r="D43" s="46">
         <f t="shared" ref="D43:M44" si="13">D22+D25+D28+D31+D34+D37</f>
         <v>261.72500000000002</v>
@@ -40055,10 +40053,10 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="179" t="s">
+      <c r="B44" s="183" t="s">
         <v>341</v>
       </c>
-      <c r="C44" s="179"/>
+      <c r="C44" s="183"/>
       <c r="D44" s="46">
         <f t="shared" si="13"/>
         <v>141.82787500000001</v>
@@ -40101,10 +40099,10 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="180" t="s">
+      <c r="B45" s="184" t="s">
         <v>342</v>
       </c>
-      <c r="C45" s="180"/>
+      <c r="C45" s="184"/>
       <c r="D45" s="46">
         <f t="shared" ref="D45:M45" si="14">D43-D44</f>
         <v>119.89712500000002</v>
@@ -40147,10 +40145,10 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="179" t="s">
+      <c r="B46" s="183" t="s">
         <v>343</v>
       </c>
-      <c r="C46" s="179"/>
+      <c r="C46" s="183"/>
       <c r="D46" s="46">
         <f>Platform!C11</f>
         <v>101</v>
@@ -40193,10 +40191,10 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B47" s="181" t="s">
+      <c r="B47" s="185" t="s">
         <v>344</v>
       </c>
-      <c r="C47" s="181"/>
+      <c r="C47" s="185"/>
       <c r="D47" s="90">
         <f t="shared" ref="D47:M47" si="15">D44+D46</f>
         <v>242.82787500000001</v>
@@ -40277,19 +40275,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="190" t="s">
         <v>345</v>
       </c>
-      <c r="B2" s="194"/>
-      <c r="C2" s="194"/>
-      <c r="D2" s="195"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="192"/>
       <c r="E2" s="88"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="196" t="s">
+      <c r="A3" s="193" t="s">
         <v>313</v>
       </c>
-      <c r="B3" s="197"/>
+      <c r="B3" s="194"/>
       <c r="C3" s="92" t="s">
         <v>346</v>
       </c>
@@ -40298,10 +40296,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="188" t="s">
         <v>347</v>
       </c>
-      <c r="B4" s="192"/>
+      <c r="B4" s="189"/>
       <c r="C4" s="93" t="s">
         <v>348</v>
       </c>
@@ -40310,10 +40308,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="191" t="s">
+      <c r="A5" s="188" t="s">
         <v>350</v>
       </c>
-      <c r="B5" s="192"/>
+      <c r="B5" s="189"/>
       <c r="C5" s="95">
         <v>10</v>
       </c>
@@ -40322,10 +40320,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="191" t="s">
+      <c r="A6" s="188" t="s">
         <v>352</v>
       </c>
-      <c r="B6" s="192"/>
+      <c r="B6" s="189"/>
       <c r="C6" s="96">
         <v>0.25</v>
       </c>
@@ -40334,10 +40332,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="191" t="s">
+      <c r="A7" s="188" t="s">
         <v>354</v>
       </c>
-      <c r="B7" s="192"/>
+      <c r="B7" s="189"/>
       <c r="C7" s="96">
         <v>0.18</v>
       </c>
@@ -40346,10 +40344,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="191" t="s">
+      <c r="A8" s="188" t="s">
         <v>356</v>
       </c>
-      <c r="B8" s="192"/>
+      <c r="B8" s="189"/>
       <c r="C8" s="96">
         <v>0.04</v>
       </c>
@@ -40358,10 +40356,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="191" t="s">
+      <c r="A9" s="188" t="s">
         <v>358</v>
       </c>
-      <c r="B9" s="192"/>
+      <c r="B9" s="189"/>
       <c r="C9" s="96">
         <v>0.04</v>
       </c>
@@ -40370,10 +40368,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="191" t="s">
+      <c r="A10" s="188" t="s">
         <v>360</v>
       </c>
-      <c r="B10" s="192"/>
+      <c r="B10" s="189"/>
       <c r="C10" s="96">
         <v>0.92</v>
       </c>
@@ -40382,10 +40380,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="191" t="s">
+      <c r="A11" s="188" t="s">
         <v>362</v>
       </c>
-      <c r="B11" s="192"/>
+      <c r="B11" s="189"/>
       <c r="C11" s="95">
         <v>180</v>
       </c>
@@ -40394,10 +40392,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="191" t="s">
+      <c r="A12" s="188" t="s">
         <v>364</v>
       </c>
-      <c r="B12" s="192"/>
+      <c r="B12" s="189"/>
       <c r="C12" s="95">
         <v>45</v>
       </c>
@@ -40406,10 +40404,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="188" t="s">
         <v>366</v>
       </c>
-      <c r="B13" s="192"/>
+      <c r="B13" s="189"/>
       <c r="C13" s="95">
         <v>90</v>
       </c>
@@ -40418,10 +40416,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="191" t="s">
+      <c r="A14" s="188" t="s">
         <v>368</v>
       </c>
-      <c r="B14" s="192"/>
+      <c r="B14" s="189"/>
       <c r="C14" s="96">
         <v>0.08</v>
       </c>
@@ -40430,10 +40428,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="191" t="s">
+      <c r="A15" s="188" t="s">
         <v>370</v>
       </c>
-      <c r="B15" s="192"/>
+      <c r="B15" s="189"/>
       <c r="C15" s="96">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -40442,10 +40440,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191" t="s">
+      <c r="A16" s="188" t="s">
         <v>372</v>
       </c>
-      <c r="B16" s="192"/>
+      <c r="B16" s="189"/>
       <c r="C16" s="96">
         <v>0.03</v>
       </c>
@@ -40454,10 +40452,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="191" t="s">
+      <c r="A17" s="188" t="s">
         <v>374</v>
       </c>
-      <c r="B17" s="192"/>
+      <c r="B17" s="189"/>
       <c r="C17" s="97">
         <v>2</v>
       </c>
@@ -40466,10 +40464,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="191" t="s">
+      <c r="A18" s="188" t="s">
         <v>376</v>
       </c>
-      <c r="B18" s="192"/>
+      <c r="B18" s="189"/>
       <c r="C18" s="97">
         <v>14.25</v>
       </c>
@@ -40478,10 +40476,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="191" t="s">
+      <c r="A19" s="188" t="s">
         <v>377</v>
       </c>
-      <c r="B19" s="192"/>
+      <c r="B19" s="189"/>
       <c r="C19" s="97">
         <v>8.5500000000000007</v>
       </c>
@@ -40490,10 +40488,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="191" t="s">
+      <c r="A20" s="188" t="s">
         <v>378</v>
       </c>
-      <c r="B20" s="192"/>
+      <c r="B20" s="189"/>
       <c r="C20" s="96">
         <v>0.03</v>
       </c>
@@ -40502,10 +40500,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="191" t="s">
+      <c r="A21" s="188" t="s">
         <v>380</v>
       </c>
-      <c r="B21" s="192"/>
+      <c r="B21" s="189"/>
       <c r="C21" s="96">
         <v>0.15</v>
       </c>
@@ -40514,10 +40512,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191" t="s">
+      <c r="A22" s="188" t="s">
         <v>382</v>
       </c>
-      <c r="B22" s="192"/>
+      <c r="B22" s="189"/>
       <c r="C22" s="96">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -40526,10 +40524,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="191" t="s">
+      <c r="A23" s="188" t="s">
         <v>384</v>
       </c>
-      <c r="B23" s="192"/>
+      <c r="B23" s="189"/>
       <c r="C23" s="96" t="s">
         <v>385</v>
       </c>
@@ -40538,10 +40536,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="191" t="s">
+      <c r="A24" s="188" t="s">
         <v>387</v>
       </c>
-      <c r="B24" s="192"/>
+      <c r="B24" s="189"/>
       <c r="C24" s="97">
         <v>100</v>
       </c>
@@ -40550,10 +40548,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="184" t="s">
+      <c r="A25" s="195" t="s">
         <v>389</v>
       </c>
-      <c r="B25" s="184"/>
+      <c r="B25" s="195"/>
       <c r="C25" s="98">
         <v>1</v>
       </c>
@@ -40562,12 +40560,12 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="188" t="s">
+      <c r="A27" s="199" t="s">
         <v>391</v>
       </c>
-      <c r="B27" s="189"/>
-      <c r="C27" s="189"/>
-      <c r="D27" s="190"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="201"/>
     </row>
     <row r="28" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="99" t="s">
@@ -40576,10 +40574,10 @@
       <c r="B28" s="100" t="s">
         <v>393</v>
       </c>
-      <c r="C28" s="184">
+      <c r="C28" s="195">
         <v>0.5</v>
       </c>
-      <c r="D28" s="184"/>
+      <c r="D28" s="195"/>
     </row>
     <row r="29" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="99" t="s">
@@ -40588,70 +40586,70 @@
       <c r="B29" s="100" t="s">
         <v>395</v>
       </c>
-      <c r="C29" s="184">
+      <c r="C29" s="195">
         <v>0.7</v>
       </c>
-      <c r="D29" s="184"/>
+      <c r="D29" s="195"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="99"/>
       <c r="B30" s="100" t="s">
         <v>396</v>
       </c>
-      <c r="C30" s="184" t="s">
+      <c r="C30" s="195" t="s">
         <v>397</v>
       </c>
-      <c r="D30" s="184"/>
+      <c r="D30" s="195"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="99"/>
       <c r="B31" s="100" t="s">
         <v>398</v>
       </c>
-      <c r="C31" s="184" t="s">
+      <c r="C31" s="195" t="s">
         <v>399</v>
       </c>
-      <c r="D31" s="184"/>
+      <c r="D31" s="195"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="99"/>
       <c r="B32" s="100" t="s">
         <v>400</v>
       </c>
-      <c r="C32" s="184" t="s">
+      <c r="C32" s="195" t="s">
         <v>401</v>
       </c>
-      <c r="D32" s="184"/>
+      <c r="D32" s="195"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="99"/>
       <c r="B33" s="100" t="s">
         <v>402</v>
       </c>
-      <c r="C33" s="184" t="s">
+      <c r="C33" s="195" t="s">
         <v>403</v>
       </c>
-      <c r="D33" s="184"/>
+      <c r="D33" s="195"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="99"/>
       <c r="B34" s="100" t="s">
         <v>404</v>
       </c>
-      <c r="C34" s="184" t="s">
+      <c r="C34" s="195" t="s">
         <v>405</v>
       </c>
-      <c r="D34" s="184"/>
+      <c r="D34" s="195"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="99"/>
       <c r="B35" s="100" t="s">
         <v>406</v>
       </c>
-      <c r="C35" s="184" t="s">
+      <c r="C35" s="195" t="s">
         <v>407</v>
       </c>
-      <c r="D35" s="184"/>
+      <c r="D35" s="195"/>
     </row>
     <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="99"/>
@@ -40800,11 +40798,11 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="185" t="s">
+      <c r="A49" s="196" t="s">
         <v>433</v>
       </c>
-      <c r="B49" s="186"/>
-      <c r="C49" s="187"/>
+      <c r="B49" s="197"/>
+      <c r="C49" s="198"/>
       <c r="D49" s="99" t="s">
         <v>434</v>
       </c>
@@ -40978,6 +40976,28 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:B3"/>
@@ -40990,28 +41010,6 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
